--- a/Input/Input_final.xlsx
+++ b/Input/Input_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofwaterloo-my.sharepoint.com/personal/fbrena_uwaterloo_ca/Documents/Research/Final4/Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fernanda\Documents\CDR_Flex\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{8673A29E-022A-44F0-9B26-3EB5680CC96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{987EBD15-00E5-46F1-BB8A-6511BF3587D8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34ADCAC-5983-4E98-8D6B-8CCB9D14AC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4215" yWindow="-16320" windowWidth="29040" windowHeight="15840" tabRatio="885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4215" yWindow="-16320" windowWidth="29040" windowHeight="15840" tabRatio="885" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CDR_Demand" sheetId="6" r:id="rId1"/>
@@ -277,1586 +277,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Storage_Capacity!$B$2:$B$72</c:f>
-              <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="71"/>
-                <c:pt idx="0">
-                  <c:v>5000000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6071428.5714285709</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7142857.1428571418</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8214285.7142857127</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9285714.2857142836</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10357142.857142854</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>11428571.428571425</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>12499999.999999996</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>13571428.571428567</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>14642857.142857138</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>15714285.714285709</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>16785714.28571428</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>17857142.857142851</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>18928571.428571422</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>19999999.999999993</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>21071428.571428563</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>22142857.142857134</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>23214285.714285705</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>24285714.285714276</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>25357142.857142847</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>26428571.428571418</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>27499999.999999989</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>28571428.57142856</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>29642857.142857131</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>30714285.714285702</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>31785714.285714272</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>32857142.857142843</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>33928571.428571418</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>34999999.999999993</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>36071428.571428567</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>37142857.142857142</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>38214285.714285716</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>39285714.285714291</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>40357142.857142866</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>41428571.42857144</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>42500000.000000015</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>43571428.57142859</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>44642857.142857164</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>45714285.714285739</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>46785714.285714313</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>47857142.857142888</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>48928571.428571463</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>50000000.000000037</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>51071428.571428612</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>52142857.142857186</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>53214285.714285761</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>54285714.285714336</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>55357142.85714291</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>56428571.428571485</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>57500000.00000006</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>58571428.571428634</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>59642857.142857209</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>60714285.714285783</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>61785714.285714358</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>62857142.857142933</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>63928571.428571507</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>65000000.000000082</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>66071428.571428657</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>67142857.142857224</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>68214285.714285791</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>69285714.285714358</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>70357142.857142925</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>71428571.428571492</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>72500000.00000006</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>73571428.571428627</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>74642857.142857194</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>75714285.714285761</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>76785714.285714328</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>77857142.857142895</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>78928571.428571463</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>80000000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-73BB-49E1-8D90-F4EA052F1FB2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Storage_Capacity!$C$2:$C$72</c:f>
-              <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="71"/>
-                <c:pt idx="0">
-                  <c:v>10000000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>13428571.428571429</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>16857142.857142858</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20285714.285714287</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23714285.714285716</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>27142857.142857146</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>30571428.571428575</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>34000000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>37428571.428571425</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>40857142.857142851</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>44285714.285714276</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>47714285.714285702</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>51142857.142857127</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>54571428.571428552</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>57999999.999999978</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>61428571.428571403</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>64857142.857142828</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>68285714.285714254</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>71714285.714285687</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>75142857.142857119</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>78571428.571428552</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>81999999.999999985</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>85428571.428571418</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>88857142.857142851</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>92285714.285714284</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>95714285.714285716</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>99142857.142857149</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>102571428.57142858</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>106000000.00000001</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>109428571.42857145</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>112857142.85714288</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>116285714.28571431</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>119714285.71428575</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>123142857.14285718</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>126571428.57142861</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>130000000.00000004</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>133428571.42857148</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>136857142.8571429</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>140285714.28571433</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>143714285.71428576</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>147142857.14285719</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>150571428.57142863</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>154000000.00000006</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>157428571.42857149</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>160857142.85714293</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>164285714.28571436</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>167714285.71428579</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>171142857.14285722</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>174571428.57142866</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>178000000.00000009</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>181428571.42857152</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>184857142.85714296</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>188285714.28571439</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>191714285.71428582</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>195142857.14285725</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>198571428.57142869</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>202000000.00000012</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>205428571.42857155</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>208857142.85714298</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>212285714.28571442</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>215714285.71428585</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>219142857.14285728</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>222571428.57142872</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>226000000.00000015</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>229428571.42857158</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>232857142.85714301</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>236285714.28571445</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>239714285.71428588</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>243142857.14285731</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>246571428.57142875</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>250000000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-73BB-49E1-8D90-F4EA052F1FB2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Storage_Capacity!$D$2:$D$72</c:f>
-              <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="71"/>
-                <c:pt idx="0">
-                  <c:v>15000000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>20500000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>26000000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>31500000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>37000000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>42500000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>48000000</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>53500000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>59000000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>64500000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>70000000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>75500000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>81000000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>86500000</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>92000000</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>97500000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>103000000</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>108500000</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>114000000</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>119500000</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>125000000</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>130500000</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>136000000</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>141500000</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>147000000</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>152500000</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>158000000</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>163500000</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>169000000</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>174500000</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>180000000</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>185500000</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>191000000</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>196500000</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>202000000</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>207500000</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>213000000</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>218500000</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>224000000</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>229500000</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>235000000</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>240500000</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>246000000</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>251500000</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>257000000</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>262500000</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>268000000</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>273500000</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>279000000</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>284500000</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>290000000</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>295500000</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>301000000</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>306500000</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>312000000</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>317500000</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>323000000</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>328500000</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>334000000</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>339500000</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>345000000</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>350500000</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>356000000</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>361500000</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>367000000</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>372500000</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>378000000</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>383500000</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>389000000</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>394500000</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>400000000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-73BB-49E1-8D90-F4EA052F1FB2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="768262687"/>
-        <c:axId val="768280447"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="768262687"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="768280447"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="768280447"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="768262687"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFF3D21A-1D6B-8C8B-EB4D-BC4E206F455E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5110,7 +3530,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
